--- a/Dashboard Xbox.xlsx
+++ b/Dashboard Xbox.xlsx
@@ -2,34 +2,33 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\caio.navia\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{22BEE5AB-39AD-4B4C-959C-4DAC3DDA3DB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD3C56B4-50F8-4B33-ADA2-80A580080919}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="481" firstSheet="2" activeTab="4" xr2:uid="{28DD5B76-0634-4F87-BE60-8BFA7EF2E23B}"/>
+    <workbookView xWindow="-19310" yWindow="-690" windowWidth="19420" windowHeight="11500" tabRatio="481" firstSheet="3" activeTab="3" xr2:uid="{28DD5B76-0634-4F87-BE60-8BFA7EF2E23B}"/>
   </bookViews>
   <sheets>
     <sheet name="A̳ssets" sheetId="1" state="hidden" r:id="rId1"/>
     <sheet name="B̳ases" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet name="C̳álculos" sheetId="3" r:id="rId3"/>
-    <sheet name="D̳ashboard_Plan_Type" sheetId="5" r:id="rId4"/>
-    <sheet name="D̳ashboard_Subscription_Type" sheetId="4" r:id="rId5"/>
+    <sheet name="C̳álculos" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet name="D̳ashboard" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="Slicer_Subscription_Type">#N/A</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="8" r:id="rId6"/>
+    <pivotCache cacheId="0" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
       <x14:slicerCaches>
-        <x14:slicerCache r:id="rId7"/>
+        <x14:slicerCache r:id="rId6"/>
       </x14:slicerCaches>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
@@ -54,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2026" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2026" uniqueCount="325">
   <si>
     <t>Paleta de Cores</t>
   </si>
@@ -1106,6 +1105,43 @@
   <si>
     <t>Sum of Minecraft Season Pass Price</t>
   </si>
+  <si>
+    <r>
+      <t>Pergunta de Negócio 1 - Qual faturamento</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Total de Vendas</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>por tipo de plano</t>
+    </r>
+  </si>
 </sst>
 </file>
 
@@ -1113,7 +1149,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="2">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="&quot;R$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -1269,15 +1305,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="3"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="3" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="3"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Currency" xfId="2" builtinId="4"/>
@@ -1290,6 +1326,7 @@
       <font>
         <b/>
         <i val="0"/>
+        <sz val="9"/>
         <color theme="0"/>
       </font>
       <border>
@@ -1385,7 +1422,239 @@
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{46F421CA-312F-682f-3DD2-61675219B42D}">
-      <x14:dxfs count="8">
+      <x14:dxfs count="16">
+        <dxf>
+          <font>
+            <color rgb="FF000000"/>
+          </font>
+          <fill>
+            <gradientFill degree="90">
+              <stop position="0">
+                <color rgb="FFF8E162"/>
+              </stop>
+              <stop position="1">
+                <color rgb="FFFCF7E0"/>
+              </stop>
+            </gradientFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FF999999"/>
+            </left>
+            <right style="thin">
+              <color rgb="FF999999"/>
+            </right>
+            <top style="thin">
+              <color rgb="FF999999"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FF999999"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF000000"/>
+          </font>
+          <fill>
+            <gradientFill degree="90">
+              <stop position="0">
+                <color rgb="FFF8E162"/>
+              </stop>
+              <stop position="1">
+                <color rgb="FFFCF7E0"/>
+              </stop>
+            </gradientFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FF999999"/>
+            </left>
+            <right style="thin">
+              <color rgb="FF999999"/>
+            </right>
+            <top style="thin">
+              <color rgb="FF999999"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FF999999"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF000000"/>
+          </font>
+          <fill>
+            <gradientFill degree="90">
+              <stop position="0">
+                <color rgb="FFF8E162"/>
+              </stop>
+              <stop position="1">
+                <color rgb="FFFCF7E0"/>
+              </stop>
+            </gradientFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FF999999"/>
+            </left>
+            <right style="thin">
+              <color rgb="FF999999"/>
+            </right>
+            <top style="thin">
+              <color rgb="FF999999"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FF999999"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF000000"/>
+          </font>
+          <fill>
+            <gradientFill degree="90">
+              <stop position="0">
+                <color rgb="FFF8E162"/>
+              </stop>
+              <stop position="1">
+                <color rgb="FFFCF7E0"/>
+              </stop>
+            </gradientFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FF999999"/>
+            </left>
+            <right style="thin">
+              <color rgb="FF999999"/>
+            </right>
+            <top style="thin">
+              <color rgb="FF999999"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FF999999"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF828282"/>
+          </font>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor theme="9" tint="0.79998168889431442"/>
+              <bgColor theme="9" tint="0.79998168889431442"/>
+            </patternFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FFCCCCCC"/>
+            </left>
+            <right style="thin">
+              <color rgb="FFCCCCCC"/>
+            </right>
+            <top style="thin">
+              <color rgb="FFCCCCCC"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FFCCCCCC"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF000000"/>
+          </font>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor theme="9" tint="0.59999389629810485"/>
+              <bgColor theme="9" tint="0.59999389629810485"/>
+            </patternFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FF999999"/>
+            </left>
+            <right style="thin">
+              <color rgb="FF999999"/>
+            </right>
+            <top style="thin">
+              <color rgb="FF999999"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FF999999"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF828282"/>
+          </font>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor rgb="FFFFFFFF"/>
+              <bgColor rgb="FFFFFFFF"/>
+            </patternFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FFE0E0E0"/>
+            </left>
+            <right style="thin">
+              <color rgb="FFE0E0E0"/>
+            </right>
+            <top style="thin">
+              <color rgb="FFE0E0E0"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FFE0E0E0"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF000000"/>
+          </font>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor rgb="FFFFFFFF"/>
+              <bgColor rgb="FFFFFFFF"/>
+            </patternFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FFCCCCCC"/>
+            </left>
+            <right style="thin">
+              <color rgb="FFCCCCCC"/>
+            </right>
+            <top style="thin">
+              <color rgb="FFCCCCCC"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FFCCCCCC"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
         <dxf>
           <font>
             <color rgb="FF000000"/>
@@ -2032,7 +2301,7 @@
         <c:delete val="1"/>
         <c:axPos val="b"/>
         <c:numFmt formatCode="_(&quot;R$&quot;* #,##0.00_);_(&quot;R$&quot;* \(#,##0.00\);_(&quot;R$&quot;* &quot;-&quot;??_);_(@_)" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="1699534511"/>
@@ -3099,8 +3368,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="1055414" y="5238092"/>
-          <a:ext cx="1556592" cy="723025"/>
+          <a:off x="1056399" y="5238092"/>
+          <a:ext cx="1546849" cy="726200"/>
           <a:chOff x="3495675" y="5400674"/>
           <a:chExt cx="1549476" cy="752476"/>
         </a:xfrm>
@@ -3388,1084 +3657,6 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>334481</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>87393</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>350586</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>106434</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Imagem 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9BE5D39D-FC66-4934-99B5-B21E37635B02}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect l="7013" t="16110" r="71537" b="19108"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2382356" y="268368"/>
-          <a:ext cx="520930" cy="504816"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>419851</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>33981</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>285750</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>9883</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="4" name="Group 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{39F45A4E-F33A-4491-9FE4-DB8BF36E2F09}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="2467726" y="1383356"/>
-          <a:ext cx="2809124" cy="1242727"/>
-          <a:chOff x="2411157" y="1112044"/>
-          <a:chExt cx="4199081" cy="1285608"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="5" name="Rectangle: Rounded Corners 4">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5E2925D-2168-41F0-3911-982DCD2E5F0D}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="2421329" y="1112045"/>
-            <a:ext cx="4188909" cy="1285607"/>
-          </a:xfrm>
-          <a:prstGeom prst="roundRect">
-            <a:avLst>
-              <a:gd name="adj" fmla="val 10478"/>
-            </a:avLst>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:schemeClr val="bg1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr lang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="C̳álculos!J42">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="6" name="Rectangle: Rounded Corners 5">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D194EED3-83C4-C486-E9C5-A52C7A0AC414}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="2411157" y="1501716"/>
-            <a:ext cx="4109371" cy="830568"/>
-          </a:xfrm>
-          <a:prstGeom prst="roundRect">
-            <a:avLst>
-              <a:gd name="adj" fmla="val 28406"/>
-            </a:avLst>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:fld id="{6FF90C97-C217-4740-90B0-C49DDFAACA18}" type="TxLink">
-              <a:rPr lang="en-US" sz="3200" b="0" i="0" u="none" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="22C55E"/>
-                </a:solidFill>
-                <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
-                <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
-              </a:rPr>
-              <a:t>R$ 120,00</a:t>
-            </a:fld>
-            <a:endParaRPr lang="en-US" sz="3200" b="0">
-              <a:solidFill>
-                <a:srgbClr val="22C55E"/>
-              </a:solidFill>
-              <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
-            </a:endParaRPr>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="8" name="Rectangle: Top Corners Rounded 7">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CFA84B0A-C84D-95ED-D850-997398D64C5B}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="2419265" y="1112044"/>
-            <a:ext cx="4183942" cy="403197"/>
-          </a:xfrm>
-          <a:prstGeom prst="round2SameRect">
-            <a:avLst>
-              <a:gd name="adj1" fmla="val 26021"/>
-              <a:gd name="adj2" fmla="val 0"/>
-            </a:avLst>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="22C55E"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr lang="en-US" sz="1100" b="1">
-                <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
-                <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
-              </a:rPr>
-              <a:t>TOTAL</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" sz="1100" b="1" baseline="0">
-                <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
-                <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
-              </a:rPr>
-              <a:t> CORE SUBSCRIPTION</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US" sz="1100" b="1">
-              <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
-            </a:endParaRPr>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>734274</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>125823</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>1303576</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>192411</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="21" name="Elipse 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E945AB06-854A-4FC0-8212-8D37E9A62449}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="734274" y="306798"/>
-          <a:ext cx="569302" cy="552363"/>
-        </a:xfrm>
-        <a:prstGeom prst="ellipse">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </a:blipFill>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="pt-BR" sz="1100" kern="1200"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>212481</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>282597</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>1831731</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>66569</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="22" name="Rectangle: Top Corners Rounded 21">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E9F0A000-262A-4B27-9DCE-B99B0FEB7C2D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="212481" y="949347"/>
-          <a:ext cx="1619250" cy="288797"/>
-        </a:xfrm>
-        <a:prstGeom prst="round2SameRect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="1">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>&gt;</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="1" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t> b</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="1">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>em</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="1" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t> vinda, Liana</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1100" b="1">
-            <a:solidFill>
-              <a:schemeClr val="bg1"/>
-            </a:solidFill>
-            <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
-            <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>401706</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>53220</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>211206</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>66897</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="23" name="TextBox 22">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED7C54B0-1B24-4C26-B922-814960EE7BB7}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2449581" y="1040645"/>
-          <a:ext cx="8696325" cy="194652"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="bg2">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Calculation period:</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg2">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-            </a:rPr>
-            <a:t> 01/01/2024 - 31/12/2024 | Update date: 18/10/2026 09:00:00</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1100">
-            <a:solidFill>
-              <a:schemeClr val="bg2">
-                <a:lumMod val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>473826</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>30806</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>234950</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>13058</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="24" name="Group 23">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{20CD22D7-C1B0-84F0-FB49-83C8271346C8}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="5464926" y="1380181"/>
-          <a:ext cx="2812299" cy="1249077"/>
-          <a:chOff x="2411157" y="1112044"/>
-          <a:chExt cx="4199081" cy="1285608"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="25" name="Rectangle: Rounded Corners 24">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{62F4184E-29DD-AEEF-54A8-BF676D7FE5A7}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="2421329" y="1112045"/>
-            <a:ext cx="4188909" cy="1285607"/>
-          </a:xfrm>
-          <a:prstGeom prst="roundRect">
-            <a:avLst>
-              <a:gd name="adj" fmla="val 10478"/>
-            </a:avLst>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:schemeClr val="bg1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr lang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="C̳álculos!J43">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="26" name="Rectangle: Rounded Corners 25">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9FC7343D-BAD1-C9B2-5095-AEF3995A17A6}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="2411157" y="1501716"/>
-            <a:ext cx="4109371" cy="830568"/>
-          </a:xfrm>
-          <a:prstGeom prst="roundRect">
-            <a:avLst>
-              <a:gd name="adj" fmla="val 28406"/>
-            </a:avLst>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:fld id="{C1E0B832-E75B-40DC-82FF-C6A1FE241BDF}" type="TxLink">
-              <a:rPr lang="en-US" sz="3200" b="0" i="0" u="none" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="22C55E"/>
-                </a:solidFill>
-                <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
-                <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
-              </a:rPr>
-              <a:t>R$ 448,00</a:t>
-            </a:fld>
-            <a:endParaRPr lang="en-US" sz="3200" b="0">
-              <a:solidFill>
-                <a:srgbClr val="22C55E"/>
-              </a:solidFill>
-              <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
-            </a:endParaRPr>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="27" name="Rectangle: Top Corners Rounded 26">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{19CDC1FD-FF53-9EE2-71FD-F27666244C03}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="2419265" y="1112044"/>
-            <a:ext cx="4183942" cy="403197"/>
-          </a:xfrm>
-          <a:prstGeom prst="round2SameRect">
-            <a:avLst>
-              <a:gd name="adj1" fmla="val 26021"/>
-              <a:gd name="adj2" fmla="val 0"/>
-            </a:avLst>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="22C55E"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr lang="en-US" sz="1100" b="1">
-                <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
-                <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
-              </a:rPr>
-              <a:t>TOTAL</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" sz="1100" b="1" baseline="0">
-                <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
-                <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
-              </a:rPr>
-              <a:t> STANDARD SUBSCRIPTION</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US" sz="1100" b="1">
-              <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
-            </a:endParaRPr>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>435726</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>30806</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>13058</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="28" name="Group 27">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A9148E0-BF7A-63B8-1EDC-238913E73922}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="8474826" y="1380181"/>
-          <a:ext cx="2809124" cy="1249077"/>
-          <a:chOff x="2411157" y="1112044"/>
-          <a:chExt cx="4199081" cy="1285608"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="29" name="Rectangle: Rounded Corners 28">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9DEF8F7-94E9-3F24-1872-4066F1796890}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="2421329" y="1112045"/>
-            <a:ext cx="4188909" cy="1285607"/>
-          </a:xfrm>
-          <a:prstGeom prst="roundRect">
-            <a:avLst>
-              <a:gd name="adj" fmla="val 10478"/>
-            </a:avLst>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:schemeClr val="bg1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr lang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="C̳álculos!J44">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="30" name="Rectangle: Rounded Corners 29">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8718A99C-4BDC-B54F-0AB5-79E20C1D863C}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="2411157" y="1501716"/>
-            <a:ext cx="4109371" cy="830568"/>
-          </a:xfrm>
-          <a:prstGeom prst="roundRect">
-            <a:avLst>
-              <a:gd name="adj" fmla="val 28406"/>
-            </a:avLst>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:fld id="{9D9E1ECF-5BAA-40B8-81BB-87F880893ABE}" type="TxLink">
-              <a:rPr lang="en-US" sz="3200" b="0" i="0" u="none" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="22C55E"/>
-                </a:solidFill>
-                <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
-                <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
-              </a:rPr>
-              <a:t>R$ 1.186,00</a:t>
-            </a:fld>
-            <a:endParaRPr lang="en-US" sz="3200" b="0">
-              <a:solidFill>
-                <a:srgbClr val="22C55E"/>
-              </a:solidFill>
-              <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
-            </a:endParaRPr>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="31" name="Rectangle: Top Corners Rounded 30">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{836D0BA6-4300-686A-64AA-554AC7193F18}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="2419265" y="1112044"/>
-            <a:ext cx="4183942" cy="403197"/>
-          </a:xfrm>
-          <a:prstGeom prst="round2SameRect">
-            <a:avLst>
-              <a:gd name="adj1" fmla="val 26021"/>
-              <a:gd name="adj2" fmla="val 0"/>
-            </a:avLst>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="22C55E"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr lang="en-US" sz="1100" b="1">
-                <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
-                <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
-              </a:rPr>
-              <a:t>TOTAL</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" sz="1100" b="1" baseline="0">
-                <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
-                <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
-              </a:rPr>
-              <a:t> ULTIMATE SUBSCRIPTION</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US" sz="1100" b="1">
-              <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
-            </a:endParaRPr>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>107164</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>56830</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>1888150</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>114774</xdr:rowOff>
-    </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-        <xdr:graphicFrame macro="">
-          <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="32" name="Subscription Type 1">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{95027C85-AB08-47D4-8363-593D09234E85}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvGraphicFramePr/>
-          </xdr:nvGraphicFramePr>
-          <xdr:xfrm>
-            <a:off x="0" y="0"/>
-            <a:ext cx="0" cy="0"/>
-          </xdr:xfrm>
-          <a:graphic>
-            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
-              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Subscription Type 1"/>
-            </a:graphicData>
-          </a:graphic>
-        </xdr:graphicFrame>
-      </mc:Choice>
-      <mc:Fallback>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="0" name=""/>
-            <xdr:cNvSpPr>
-              <a:spLocks noTextEdit="1"/>
-            </xdr:cNvSpPr>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="103989" y="1409380"/>
-              <a:ext cx="1784161" cy="1324769"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:solidFill>
-              <a:prstClr val="white"/>
-            </a:solidFill>
-            <a:ln w="1">
-              <a:solidFill>
-                <a:prstClr val="green"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100"/>
-                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
-If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
       <xdr:colOff>331306</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>84218</xdr:rowOff>
@@ -4517,15 +3708,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>123605</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>47239</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>59689</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>1907766</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>105183</xdr:rowOff>
+      <xdr:colOff>1979706</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>117634</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
@@ -4561,8 +3752,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="126780" y="1395120"/>
-              <a:ext cx="1780986" cy="1306653"/>
+              <a:off x="0" y="1616062"/>
+              <a:ext cx="1979706" cy="1365297"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -4618,8 +3809,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="2327135" y="3269936"/>
-          <a:ext cx="4162185" cy="1379379"/>
+          <a:off x="2327696" y="3369544"/>
+          <a:ext cx="4201467" cy="1439144"/>
           <a:chOff x="2419265" y="1112044"/>
           <a:chExt cx="4183942" cy="1422427"/>
         </a:xfrm>
@@ -4869,8 +4060,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="6916666" y="3269161"/>
-          <a:ext cx="4145770" cy="1235786"/>
+          <a:off x="6964664" y="3368769"/>
+          <a:ext cx="4176898" cy="1288080"/>
           <a:chOff x="7077075" y="1104107"/>
           <a:chExt cx="4170385" cy="1241910"/>
         </a:xfrm>
@@ -4983,6 +4174,7 @@
                 <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
                 <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
               </a:rPr>
+              <a:pPr algn="ctr"/>
               <a:t>R$ 940,00</a:t>
             </a:fld>
             <a:endParaRPr lang="en-US" sz="3200" b="1">
@@ -5174,8 +4366,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="2327135" y="4797240"/>
-          <a:ext cx="8766483" cy="3048506"/>
+          <a:off x="2327696" y="4967258"/>
+          <a:ext cx="8841873" cy="3175506"/>
           <a:chOff x="2453143" y="2613744"/>
           <a:chExt cx="8807793" cy="3067686"/>
         </a:xfrm>
@@ -5331,8 +4523,19 @@
                 <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
                 <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
               </a:rPr>
-              <a:t>TOTAL SUBSCRIPTION XBOX GAME PASS</a:t>
+              <a:t>TOTAL SUBSCRIPTION XBOX GAME PASS | AUTO</a:t>
             </a:r>
+            <a:r>
+              <a:rPr lang="en-US" sz="1100" b="1" baseline="0">
+                <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t> RENEWAL</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" sz="1100" b="1">
+              <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+            </a:endParaRPr>
           </a:p>
         </xdr:txBody>
       </xdr:sp>
@@ -5631,8 +4834,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="2323960" y="1587923"/>
-          <a:ext cx="2786553" cy="1240486"/>
+          <a:off x="2330871" y="1623471"/>
+          <a:ext cx="2809524" cy="1286429"/>
           <a:chOff x="2411157" y="1112044"/>
           <a:chExt cx="4199081" cy="1285608"/>
         </a:xfrm>
@@ -5738,16 +4941,17 @@
           <a:p>
             <a:pPr algn="ctr"/>
             <a:fld id="{6FF90C97-C217-4740-90B0-C49DDFAACA18}" type="TxLink">
-              <a:rPr lang="en-US" sz="3200" b="0" i="0" u="none" strike="noStrike">
+              <a:rPr lang="en-US" sz="3200" b="1" i="0" u="none" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="22C55E"/>
                 </a:solidFill>
                 <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
                 <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
               </a:rPr>
+              <a:pPr algn="ctr"/>
               <a:t>R$ 120,00</a:t>
             </a:fld>
-            <a:endParaRPr lang="en-US" sz="3200" b="0">
+            <a:endParaRPr lang="en-US" sz="3200" b="1">
               <a:solidFill>
                 <a:srgbClr val="22C55E"/>
               </a:solidFill>
@@ -5857,8 +5061,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="5210596" y="1591098"/>
-          <a:ext cx="2802587" cy="1234136"/>
+          <a:off x="5243653" y="1620296"/>
+          <a:ext cx="2821139" cy="1292779"/>
           <a:chOff x="2411157" y="1112044"/>
           <a:chExt cx="4199081" cy="1285608"/>
         </a:xfrm>
@@ -5964,16 +5168,17 @@
           <a:p>
             <a:pPr algn="ctr"/>
             <a:fld id="{C1E0B832-E75B-40DC-82FF-C6A1FE241BDF}" type="TxLink">
-              <a:rPr lang="en-US" sz="3200" b="0" i="0" u="none" strike="noStrike">
+              <a:rPr lang="en-US" sz="3200" b="1" i="0" u="none" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="22C55E"/>
                 </a:solidFill>
                 <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
                 <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
               </a:rPr>
+              <a:pPr algn="ctr"/>
               <a:t>R$ 448,00</a:t>
             </a:fld>
-            <a:endParaRPr lang="en-US" sz="3200" b="0">
+            <a:endParaRPr lang="en-US" sz="3200" b="1">
               <a:solidFill>
                 <a:srgbClr val="22C55E"/>
               </a:solidFill>
@@ -6083,8 +5288,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="8218041" y="1587924"/>
-          <a:ext cx="2802962" cy="1240485"/>
+          <a:off x="8276000" y="1617122"/>
+          <a:ext cx="2824129" cy="1299128"/>
           <a:chOff x="2411157" y="1112045"/>
           <a:chExt cx="4199081" cy="1285607"/>
         </a:xfrm>
@@ -6190,16 +5395,17 @@
           <a:p>
             <a:pPr algn="ctr"/>
             <a:fld id="{9D9E1ECF-5BAA-40B8-81BB-87F880893ABE}" type="TxLink">
-              <a:rPr lang="en-US" sz="3200" b="0" i="0" u="none" strike="noStrike">
+              <a:rPr lang="en-US" sz="3200" b="1" i="0" u="none" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="22C55E"/>
                 </a:solidFill>
                 <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
                 <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
               </a:rPr>
+              <a:pPr algn="ctr"/>
               <a:t>R$ 1.186,00</a:t>
             </a:fld>
-            <a:endParaRPr lang="en-US" sz="3200" b="0">
+            <a:endParaRPr lang="en-US" sz="3200" b="1">
               <a:solidFill>
                 <a:srgbClr val="22C55E"/>
               </a:solidFill>
@@ -10797,7 +10003,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8C68A9A8-29BA-4BF9-A4D5-2949D60395C8}" name="plan_types" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8C68A9A8-29BA-4BF9-A4D5-2949D60395C8}" name="plan_types" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C40:D44" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="13">
     <pivotField showAll="0"/>
@@ -10819,11 +10025,11 @@
       </items>
     </pivotField>
     <pivotField numFmtId="44" showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
       <items count="4">
         <item x="1"/>
-        <item x="2"/>
-        <item x="0"/>
+        <item h="1" x="2"/>
+        <item h="1" x="0"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -10870,7 +10076,7 @@
     <i/>
   </colItems>
   <pageFields count="1">
-    <pageField fld="6" item="0" hier="-1"/>
+    <pageField fld="6" hier="-1"/>
   </pageFields>
   <dataFields count="1">
     <dataField name="Sum of Total Value" fld="12" baseField="0" baseItem="0" numFmtId="44"/>
@@ -10888,7 +10094,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5F789F38-E641-41DC-92AC-901919A36B81}" name="PivotTable3" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5F789F38-E641-41DC-92AC-901919A36B81}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
   <location ref="C30:D34" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="13">
     <pivotField showAll="0"/>
@@ -10910,11 +10116,11 @@
       </items>
     </pivotField>
     <pivotField numFmtId="44" showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
       <items count="4">
         <item x="1"/>
-        <item x="0"/>
-        <item x="2"/>
+        <item h="1" x="0"/>
+        <item h="1" x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -10952,7 +10158,7 @@
     <i/>
   </colItems>
   <pageFields count="1">
-    <pageField fld="6" item="0" hier="-1"/>
+    <pageField fld="6" hier="-1"/>
   </pageFields>
   <dataFields count="1">
     <dataField name="Sum of Minecraft Season Pass Price" fld="10" baseField="0" baseItem="0" numFmtId="44"/>
@@ -10970,7 +10176,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A404DF44-7F38-4A16-8A4B-7A14893F85BA}" name="tbl_easeasonpass_total" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A404DF44-7F38-4A16-8A4B-7A14893F85BA}" name="tbl_easeasonpass_total" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
   <location ref="C21:C22" firstHeaderRow="1" firstDataRow="1" firstDataCol="0" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="13">
     <pivotField showAll="0"/>
@@ -10992,11 +10198,11 @@
       </items>
     </pivotField>
     <pivotField numFmtId="44" showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
       <items count="4">
         <item x="1"/>
-        <item x="0"/>
-        <item x="2"/>
+        <item h="1" x="0"/>
+        <item h="1" x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -11020,7 +10226,7 @@
     <i/>
   </colItems>
   <pageFields count="1">
-    <pageField fld="6" item="0" hier="-1"/>
+    <pageField fld="6" hier="-1"/>
   </pageFields>
   <dataFields count="1">
     <dataField name="Sum of EA Play Season Pass" fld="8" baseField="2" baseItem="0"/>
@@ -11038,7 +10244,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8F84C4C8-9F0B-493C-A4AF-2FA9EECF44DC}" name="tbl_annual_total" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8F84C4C8-9F0B-493C-A4AF-2FA9EECF44DC}" name="tbl_annual_total" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
   <location ref="C11:D14" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="13">
     <pivotField showAll="0"/>
@@ -11053,11 +10259,11 @@
       </items>
     </pivotField>
     <pivotField numFmtId="44" showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
       <items count="4">
         <item x="1"/>
-        <item x="0"/>
-        <item x="2"/>
+        <item h="1" x="0"/>
+        <item h="1" x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -11086,7 +10292,7 @@
     <i/>
   </colItems>
   <pageFields count="1">
-    <pageField fld="6" item="0" hier="-1"/>
+    <pageField fld="6" hier="-1"/>
   </pageFields>
   <dataFields count="1">
     <dataField name="Sum of Total Value" fld="12" baseField="0" baseItem="0" numFmtId="44"/>
@@ -11153,12 +10359,6 @@
 </file>
 
 <file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
-<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
-  <slicer name="Subscription Type 1" xr10:uid="{E635C38F-0BF5-460C-BA57-7A69AC405247}" cache="Slicer_Subscription_Type" caption="Subscription Type" style="SlicerStyleLight6 2" rowHeight="251883"/>
-</slicers>
-</file>
-
-<file path=xl/slicers/slicer2.xml><?xml version="1.0" encoding="utf-8"?>
 <slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
   <slicer name="Subscription Type" xr10:uid="{2E8DAAC1-C001-45EF-91DB-53E946258C15}" cache="Slicer_Subscription_Type" caption="Subscription Type" style="SlicerStyleLight6 2" rowHeight="251883"/>
 </slicers>
@@ -23845,8 +23045,8 @@
   <dimension ref="C3:J44"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="15.90625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.26953125" bestFit="1" customWidth="1"/>
     <col min="5" max="9" width="11.7265625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10.36328125" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="10.1796875" bestFit="1" customWidth="1"/>
@@ -23858,12 +23058,17 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="18" t="s">
         <v>309</v>
       </c>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+    </row>
+    <row r="5" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C5" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="6" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C6" t="s">
@@ -23934,10 +23139,10 @@
       </c>
     </row>
     <row r="22" spans="3:7" x14ac:dyDescent="0.35">
-      <c r="C22" s="17">
+      <c r="C22" s="19">
         <v>600</v>
       </c>
-      <c r="G22" s="18">
+      <c r="G22" s="16">
         <f>GETPIVOTDATA("EA Play Season Pass
 Price",$C$21)</f>
         <v>600</v>
@@ -23995,7 +23200,7 @@
       <c r="D34" s="13">
         <v>940</v>
       </c>
-      <c r="G34" s="18">
+      <c r="G34" s="16">
         <f>GETPIVOTDATA("Minecraft Season Pass Price",$C$30)</f>
         <v>940</v>
       </c>
@@ -24031,7 +23236,7 @@
       <c r="D42" s="13">
         <v>448</v>
       </c>
-      <c r="J42" s="18">
+      <c r="J42" s="16">
         <f>GETPIVOTDATA("Total Value",$C$40,"Plan","Core")</f>
         <v>120</v>
       </c>
@@ -24043,7 +23248,7 @@
       <c r="D43" s="13">
         <v>1186</v>
       </c>
-      <c r="J43" s="18">
+      <c r="J43" s="16">
         <f>GETPIVOTDATA("Total Value",$C$40,"Plan","Standard")</f>
         <v>448</v>
       </c>
@@ -24055,7 +23260,7 @@
       <c r="D44" s="13">
         <v>1754</v>
       </c>
-      <c r="J44" s="18">
+      <c r="J44" s="16">
         <f>GETPIVOTDATA("Total Value",$C$40,"Plan","Ultimate")</f>
         <v>1186</v>
       </c>
@@ -24070,816 +23275,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAA3678E-B5C6-43FA-89C3-B8B75F1CB952}">
-  <dimension ref="A1:Q256"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.5" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="29.36328125" style="4" customWidth="1"/>
-    <col min="2" max="2" width="7.26953125" customWidth="1"/>
-    <col min="3" max="11" width="8.7265625" customWidth="1"/>
-    <col min="12" max="12" width="6.54296875" customWidth="1"/>
-    <col min="13" max="16" width="8.7265625" customWidth="1"/>
-    <col min="17" max="17" width="4.90625" customWidth="1"/>
-    <col min="18" max="18" width="8.7265625" customWidth="1"/>
-    <col min="19" max="16384" width="8.7265625" hidden="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="1:17" ht="38.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="C2" s="19" t="s">
-        <v>319</v>
-      </c>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-      <c r="O2" s="16"/>
-      <c r="P2" s="16"/>
-      <c r="Q2" s="16"/>
-    </row>
-    <row r="3" spans="1:17" ht="25.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35"/>
-    <row r="4" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="4"/>
-    </row>
-    <row r="5" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="4"/>
-    </row>
-    <row r="6" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="4"/>
-    </row>
-    <row r="7" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="4"/>
-    </row>
-    <row r="8" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="4"/>
-    </row>
-    <row r="9" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="4"/>
-    </row>
-    <row r="10" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="4"/>
-    </row>
-    <row r="11" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="4"/>
-    </row>
-    <row r="12" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="4"/>
-    </row>
-    <row r="13" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="4"/>
-    </row>
-    <row r="14" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="4"/>
-    </row>
-    <row r="15" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="4"/>
-    </row>
-    <row r="16" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="4"/>
-    </row>
-    <row r="17" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="4"/>
-    </row>
-    <row r="18" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="4"/>
-    </row>
-    <row r="19" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="4"/>
-    </row>
-    <row r="20" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="4"/>
-    </row>
-    <row r="21" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="4"/>
-    </row>
-    <row r="22" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="4"/>
-    </row>
-    <row r="23" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="4"/>
-    </row>
-    <row r="24" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="4"/>
-    </row>
-    <row r="25" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="4"/>
-    </row>
-    <row r="26" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="4"/>
-    </row>
-    <row r="27" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="4"/>
-    </row>
-    <row r="28" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="4"/>
-    </row>
-    <row r="29" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="4"/>
-    </row>
-    <row r="30" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="4"/>
-    </row>
-    <row r="31" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="4"/>
-    </row>
-    <row r="32" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="4"/>
-    </row>
-    <row r="33" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="4"/>
-    </row>
-    <row r="34" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="4"/>
-    </row>
-    <row r="35" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="4"/>
-    </row>
-    <row r="36" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="4"/>
-    </row>
-    <row r="37" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="4"/>
-    </row>
-    <row r="38" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="4"/>
-    </row>
-    <row r="39" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="4"/>
-    </row>
-    <row r="40" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="4"/>
-    </row>
-    <row r="41" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="4"/>
-    </row>
-    <row r="42" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="4"/>
-    </row>
-    <row r="43" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="4"/>
-    </row>
-    <row r="44" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="4"/>
-    </row>
-    <row r="45" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="4"/>
-    </row>
-    <row r="46" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="4"/>
-    </row>
-    <row r="47" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="4"/>
-    </row>
-    <row r="48" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="4"/>
-    </row>
-    <row r="49" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="4"/>
-    </row>
-    <row r="50" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="4"/>
-    </row>
-    <row r="51" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="4"/>
-    </row>
-    <row r="52" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="4"/>
-    </row>
-    <row r="53" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="4"/>
-    </row>
-    <row r="54" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="4"/>
-    </row>
-    <row r="55" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="4"/>
-    </row>
-    <row r="56" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="4"/>
-    </row>
-    <row r="57" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="4"/>
-    </row>
-    <row r="58" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="4"/>
-    </row>
-    <row r="59" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="4"/>
-    </row>
-    <row r="60" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="4"/>
-    </row>
-    <row r="61" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="4"/>
-    </row>
-    <row r="62" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="4"/>
-    </row>
-    <row r="63" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="4"/>
-    </row>
-    <row r="64" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="4"/>
-    </row>
-    <row r="65" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="4"/>
-    </row>
-    <row r="66" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="4"/>
-    </row>
-    <row r="67" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="4"/>
-    </row>
-    <row r="68" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="4"/>
-    </row>
-    <row r="69" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="4"/>
-    </row>
-    <row r="70" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="4"/>
-    </row>
-    <row r="71" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="4"/>
-    </row>
-    <row r="72" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="4"/>
-    </row>
-    <row r="73" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="4"/>
-    </row>
-    <row r="74" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="4"/>
-    </row>
-    <row r="75" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="4"/>
-    </row>
-    <row r="76" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="4"/>
-    </row>
-    <row r="77" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="4"/>
-    </row>
-    <row r="78" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="4"/>
-    </row>
-    <row r="79" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="4"/>
-    </row>
-    <row r="80" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="4"/>
-    </row>
-    <row r="81" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="4"/>
-    </row>
-    <row r="82" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="4"/>
-    </row>
-    <row r="83" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A83" s="4"/>
-    </row>
-    <row r="84" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="4"/>
-    </row>
-    <row r="85" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="4"/>
-    </row>
-    <row r="86" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="4"/>
-    </row>
-    <row r="87" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="4"/>
-    </row>
-    <row r="88" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="4"/>
-    </row>
-    <row r="89" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="4"/>
-    </row>
-    <row r="90" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="4"/>
-    </row>
-    <row r="91" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="4"/>
-    </row>
-    <row r="92" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="4"/>
-    </row>
-    <row r="93" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="4"/>
-    </row>
-    <row r="94" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="4"/>
-    </row>
-    <row r="95" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="4"/>
-    </row>
-    <row r="96" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="4"/>
-    </row>
-    <row r="97" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="4"/>
-    </row>
-    <row r="98" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A98" s="4"/>
-    </row>
-    <row r="99" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A99" s="4"/>
-    </row>
-    <row r="100" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A100" s="4"/>
-    </row>
-    <row r="101" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A101" s="4"/>
-    </row>
-    <row r="102" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A102" s="4"/>
-    </row>
-    <row r="103" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A103" s="4"/>
-    </row>
-    <row r="104" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A104" s="4"/>
-    </row>
-    <row r="105" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A105" s="4"/>
-    </row>
-    <row r="106" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="4"/>
-    </row>
-    <row r="107" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A107" s="4"/>
-    </row>
-    <row r="108" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A108" s="4"/>
-    </row>
-    <row r="109" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A109" s="4"/>
-    </row>
-    <row r="110" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A110" s="4"/>
-    </row>
-    <row r="111" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A111" s="4"/>
-    </row>
-    <row r="112" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A112" s="4"/>
-    </row>
-    <row r="113" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A113" s="4"/>
-    </row>
-    <row r="114" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A114" s="4"/>
-    </row>
-    <row r="115" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A115" s="4"/>
-    </row>
-    <row r="116" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A116" s="4"/>
-    </row>
-    <row r="117" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A117" s="4"/>
-    </row>
-    <row r="118" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A118" s="4"/>
-    </row>
-    <row r="119" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A119" s="4"/>
-    </row>
-    <row r="120" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A120" s="4"/>
-    </row>
-    <row r="121" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A121" s="4"/>
-    </row>
-    <row r="122" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A122" s="4"/>
-    </row>
-    <row r="123" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A123" s="4"/>
-    </row>
-    <row r="124" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A124" s="4"/>
-    </row>
-    <row r="125" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A125" s="4"/>
-    </row>
-    <row r="126" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A126" s="4"/>
-    </row>
-    <row r="127" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A127" s="4"/>
-    </row>
-    <row r="128" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A128" s="4"/>
-    </row>
-    <row r="129" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A129" s="4"/>
-    </row>
-    <row r="130" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A130" s="4"/>
-    </row>
-    <row r="131" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A131" s="4"/>
-    </row>
-    <row r="132" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A132" s="4"/>
-    </row>
-    <row r="133" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A133" s="4"/>
-    </row>
-    <row r="134" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A134" s="4"/>
-    </row>
-    <row r="135" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A135" s="4"/>
-    </row>
-    <row r="136" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A136" s="4"/>
-    </row>
-    <row r="137" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A137" s="4"/>
-    </row>
-    <row r="138" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A138" s="4"/>
-    </row>
-    <row r="139" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A139" s="4"/>
-    </row>
-    <row r="140" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A140" s="4"/>
-    </row>
-    <row r="141" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A141" s="4"/>
-    </row>
-    <row r="142" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A142" s="4"/>
-    </row>
-    <row r="143" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A143" s="4"/>
-    </row>
-    <row r="144" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A144" s="4"/>
-    </row>
-    <row r="145" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A145" s="4"/>
-    </row>
-    <row r="146" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A146" s="4"/>
-    </row>
-    <row r="147" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A147" s="4"/>
-    </row>
-    <row r="148" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A148" s="4"/>
-    </row>
-    <row r="149" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A149" s="4"/>
-    </row>
-    <row r="150" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A150" s="4"/>
-    </row>
-    <row r="151" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A151" s="4"/>
-    </row>
-    <row r="152" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A152" s="4"/>
-    </row>
-    <row r="153" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A153" s="4"/>
-    </row>
-    <row r="154" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A154" s="4"/>
-    </row>
-    <row r="155" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A155" s="4"/>
-    </row>
-    <row r="156" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A156" s="4"/>
-    </row>
-    <row r="157" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A157" s="4"/>
-    </row>
-    <row r="158" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A158" s="4"/>
-    </row>
-    <row r="159" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A159" s="4"/>
-    </row>
-    <row r="160" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A160" s="4"/>
-    </row>
-    <row r="161" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A161" s="4"/>
-    </row>
-    <row r="162" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A162" s="4"/>
-    </row>
-    <row r="163" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A163" s="4"/>
-    </row>
-    <row r="164" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A164" s="4"/>
-    </row>
-    <row r="165" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A165" s="4"/>
-    </row>
-    <row r="166" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A166" s="4"/>
-    </row>
-    <row r="167" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A167" s="4"/>
-    </row>
-    <row r="168" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A168" s="4"/>
-    </row>
-    <row r="169" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A169" s="4"/>
-    </row>
-    <row r="170" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A170" s="4"/>
-    </row>
-    <row r="171" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A171" s="4"/>
-    </row>
-    <row r="172" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A172" s="4"/>
-    </row>
-    <row r="173" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A173" s="4"/>
-    </row>
-    <row r="174" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A174" s="4"/>
-    </row>
-    <row r="175" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A175" s="4"/>
-    </row>
-    <row r="176" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A176" s="4"/>
-    </row>
-    <row r="177" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A177" s="4"/>
-    </row>
-    <row r="178" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A178" s="4"/>
-    </row>
-    <row r="179" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A179" s="4"/>
-    </row>
-    <row r="180" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A180" s="4"/>
-    </row>
-    <row r="181" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A181" s="4"/>
-    </row>
-    <row r="182" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A182" s="4"/>
-    </row>
-    <row r="183" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A183" s="4"/>
-    </row>
-    <row r="184" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A184" s="4"/>
-    </row>
-    <row r="185" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A185" s="4"/>
-    </row>
-    <row r="186" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A186" s="4"/>
-    </row>
-    <row r="187" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A187" s="4"/>
-    </row>
-    <row r="188" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A188" s="4"/>
-    </row>
-    <row r="189" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A189" s="4"/>
-    </row>
-    <row r="190" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A190" s="4"/>
-    </row>
-    <row r="191" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A191" s="4"/>
-    </row>
-    <row r="192" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A192" s="4"/>
-    </row>
-    <row r="193" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A193" s="4"/>
-    </row>
-    <row r="194" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A194" s="4"/>
-    </row>
-    <row r="195" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A195" s="4"/>
-    </row>
-    <row r="196" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A196" s="4"/>
-    </row>
-    <row r="197" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A197" s="4"/>
-    </row>
-    <row r="198" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A198" s="4"/>
-    </row>
-    <row r="199" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A199" s="4"/>
-    </row>
-    <row r="200" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A200" s="4"/>
-    </row>
-    <row r="201" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A201" s="4"/>
-    </row>
-    <row r="202" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A202" s="4"/>
-    </row>
-    <row r="203" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A203" s="4"/>
-    </row>
-    <row r="204" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A204" s="4"/>
-    </row>
-    <row r="205" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A205" s="4"/>
-    </row>
-    <row r="206" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A206" s="4"/>
-    </row>
-    <row r="207" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A207" s="4"/>
-    </row>
-    <row r="208" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A208" s="4"/>
-    </row>
-    <row r="209" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A209" s="4"/>
-    </row>
-    <row r="210" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A210" s="4"/>
-    </row>
-    <row r="211" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A211" s="4"/>
-    </row>
-    <row r="212" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A212" s="4"/>
-    </row>
-    <row r="213" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A213" s="4"/>
-    </row>
-    <row r="214" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A214" s="4"/>
-    </row>
-    <row r="215" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A215" s="4"/>
-    </row>
-    <row r="216" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A216" s="4"/>
-    </row>
-    <row r="217" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A217" s="4"/>
-    </row>
-    <row r="218" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A218" s="4"/>
-    </row>
-    <row r="219" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A219" s="4"/>
-    </row>
-    <row r="220" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A220" s="4"/>
-    </row>
-    <row r="221" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A221" s="4"/>
-    </row>
-    <row r="222" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A222" s="4"/>
-    </row>
-    <row r="223" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A223" s="4"/>
-    </row>
-    <row r="224" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A224" s="4"/>
-    </row>
-    <row r="225" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A225" s="4"/>
-    </row>
-    <row r="226" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A226" s="4"/>
-    </row>
-    <row r="227" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A227" s="4"/>
-    </row>
-    <row r="228" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A228" s="4"/>
-    </row>
-    <row r="229" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A229" s="4"/>
-    </row>
-    <row r="230" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A230" s="4"/>
-    </row>
-    <row r="231" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A231" s="4"/>
-    </row>
-    <row r="232" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A232" s="4"/>
-    </row>
-    <row r="233" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A233" s="4"/>
-    </row>
-    <row r="234" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A234" s="4"/>
-    </row>
-    <row r="235" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A235" s="4"/>
-    </row>
-    <row r="236" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A236" s="4"/>
-    </row>
-    <row r="237" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A237" s="4"/>
-    </row>
-    <row r="238" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A238" s="4"/>
-    </row>
-    <row r="239" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A239" s="4"/>
-    </row>
-    <row r="240" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A240" s="4"/>
-    </row>
-    <row r="241" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A241" s="4"/>
-    </row>
-    <row r="242" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A242" s="4"/>
-    </row>
-    <row r="243" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A243" s="4"/>
-    </row>
-    <row r="244" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A244" s="4"/>
-    </row>
-    <row r="245" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A245" s="4"/>
-    </row>
-    <row r="246" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A246" s="4"/>
-    </row>
-    <row r="247" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A247" s="4"/>
-    </row>
-    <row r="248" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A248" s="4"/>
-    </row>
-    <row r="249" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A249" s="4"/>
-    </row>
-    <row r="250" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A250" s="4"/>
-    </row>
-    <row r="251" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A251" s="4"/>
-    </row>
-    <row r="252" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A252" s="4"/>
-    </row>
-    <row r="253" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A253" s="4"/>
-    </row>
-    <row r="254" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A254" s="4"/>
-    </row>
-    <row r="255" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A255" s="4"/>
-    </row>
-    <row r="256" spans="1:1" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A256" s="4"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <drawing r:id="rId1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
-      <x14:slicerList>
-        <x14:slicer r:id="rId2"/>
-      </x14:slicerList>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{210F14EF-C0B7-459D-9E09-3130BA4314A6}">
-  <dimension ref="A2:Q256"/>
+  <dimension ref="A2:R256"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="29.36328125" style="4" customWidth="1"/>
@@ -24893,23 +23290,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:17" ht="38.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="17" t="s">
         <v>319</v>
       </c>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-      <c r="O2" s="16"/>
-      <c r="P2" s="16"/>
-      <c r="Q2" s="16"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="15"/>
+      <c r="O2" s="15"/>
+      <c r="P2" s="15"/>
+      <c r="Q2" s="15"/>
     </row>
     <row r="3" spans="1:17" ht="25.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.35">
@@ -25685,15 +24082,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010001E48B58A68BE64E9120D347E3E06B3A" ma:contentTypeVersion="19" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="2f90046ec77328b7f86417d2e03b3d33">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="851b35d3-0456-4d6a-bc2f-da927e91d158" xmlns:ns3="19483571-f922-4e8e-9c1c-26f0a2252132" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c815006ac2d4f05ee97fdd57e40d8e38" ns2:_="" ns3:_="">
     <xsd:import namespace="851b35d3-0456-4d6a-bc2f-da927e91d158"/>
@@ -25948,6 +24336,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -25960,14 +24357,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3B4D9D5-B351-46EB-A728-C3362FE437D4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32608D25-EC36-42FE-A1DC-F778995A6799}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -25986,6 +24375,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3B4D9D5-B351-46EB-A728-C3362FE437D4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFD3D529-BCD3-4ECD-9B2A-42924892FFCB}">
   <ds:schemaRefs>
